--- a/template/experiment_template.xlsx
+++ b/template/experiment_template.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="実験データ" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="実験条件" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -62,15 +61,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -676,139 +672,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>ラベル</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>値</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>単位</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>実験名</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>逐次反応実験-001</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>反応物質</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>物質A→B→C</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>初期濃度</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>mol/L</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>反応温度</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>°C</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>実験日</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>担当者</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>山田太郎</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>窒素雰囲気下</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>